--- a/corpus/xlsx/level-018/template.xlsx
+++ b/corpus/xlsx/level-018/template.xlsx
@@ -94,7 +94,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -134,15 +142,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -160,55 +160,55 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">u</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">o</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">me</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">c</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">om</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -226,7 +226,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -266,15 +274,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">t}</t>
     </r>
   </si>
   <si>
@@ -292,23 +292,31 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">s</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">pa</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">sp</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">a</t>
     </r>
     <r>
       <rPr>
@@ -332,15 +340,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -358,15 +358,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">en</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.e</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">n</t>
     </r>
     <r>
       <rPr>
@@ -382,31 +390,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">b</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">le</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">bl</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -424,15 +424,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">li</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.l</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i</t>
     </r>
     <r>
       <rPr>
@@ -448,31 +456,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ra</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">er</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
 </sst>
